--- a/2022 data/excel_outputs/357_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/357_boothwise_data.xlsx
@@ -14,804 +14,1272 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="446">
   <si>
     <t>AC 357 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>######## ####### ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>### ###### ############e##0</t>
-  </si>
-  <si>
-    <t>### ###### ############e#0</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ######e ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ######e ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ##0.1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0.2 ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;#########ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #############e#0</t>
-  </si>
-  <si>
-    <t>######## ######## ###########</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0##########</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #0</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ##############e##0</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ####### #######e#0</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### #######e##0</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### #######e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ######e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ######e#0</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##0</t>
-  </si>
-  <si>
-    <t>######## ######## #### #0</t>
-  </si>
-  <si>
-    <t>############ ###### ##0e########## ;##0ddh</t>
-  </si>
-  <si>
-    <t>############ ###### ##0e########## ;#0ddh</t>
-  </si>
-  <si>
-    <t>############ ###### ##0 ########## #0</t>
-  </si>
-  <si>
-    <t>##### ######## #0##0#0##0 ########## ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ######## #0##0#0##0 ########## ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##0.2 ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##0.2 ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0e###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #############.2;######ddh</t>
-  </si>
-  <si>
-    <t>####0##0########### ####e #0</t>
-  </si>
-  <si>
-    <t>###### #0##0##0 ########### ;##0ddh</t>
-  </si>
-  <si>
-    <t>###### #0##0##0 ########### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;###########ddh #0</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>######## ##### ########### ###</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ########### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ########### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ############## ##0.1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0###### ##0</t>
-  </si>
-  <si>
-    <t>####0##0###### #0</t>
-  </si>
-  <si>
-    <t>################ ###### #### ##0.1e##0</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ##0.1e#0</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0###### ##### #### ######</t>
-  </si>
-  <si>
-    <t>####0##0#####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #############e##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #############e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ############# #0</t>
-  </si>
-  <si>
-    <t>####0##0 ############ #######</t>
-  </si>
-  <si>
-    <t>####0##0###### ##0 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ######## ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ##0</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ########## ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ########## #0</t>
-  </si>
-  <si>
-    <t>######## ####0 ####### ##### ##### ###### ##0</t>
-  </si>
-  <si>
-    <t>######## ####0 ####### ##### ##### ###### #0</t>
-  </si>
-  <si>
-    <t>####### ######## #### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ############# ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ################ #0</t>
-  </si>
-  <si>
-    <t>######## ######## ############ ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ############ ;##0ddh</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ####### ##0</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ####### #0</t>
-  </si>
-  <si>
-    <t>######## ######## #####e##0</t>
-  </si>
-  <si>
-    <t>######## ######## #####e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0</t>
-  </si>
-  <si>
-    <t>###### ### ####### ##0</t>
-  </si>
-  <si>
-    <t>###### ### ####### #0</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######;##0ddh</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######;#0ddh</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### #0</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### ### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### ### ##0</t>
-  </si>
-  <si>
-    <t>### ###### ####### ##### ### ###### ###### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #######e##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ##########</t>
-  </si>
-  <si>
-    <t>####0##0 #### #########e##0</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######### ##0</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ######e#0</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ##0</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #0</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######## #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######## ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ############# ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ############# ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>######## ######## ######e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ############# #0</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #######e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### #0</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### ###### ##0</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>##### ######## ######### ##### ##0</t>
-  </si>
-  <si>
-    <t>##### ######## ######### ##### #0</t>
-  </si>
-  <si>
-    <t>####0##0############</t>
-  </si>
-  <si>
-    <t>######## ######## #### ########e##0</t>
-  </si>
-  <si>
-    <t>######## ######## #### ########e#0</t>
-  </si>
-  <si>
-    <t>####0##0 #### #####e#0</t>
-  </si>
-  <si>
-    <t>####0##0########e##0</t>
-  </si>
-  <si>
-    <t>####0##0 #########e##0</t>
-  </si>
-  <si>
-    <t>####0##0 #########e#0</t>
-  </si>
-  <si>
-    <t>####0##0########</t>
-  </si>
-  <si>
-    <t>######## ######## ################e#0</t>
-  </si>
-  <si>
-    <t>####0##0 #####e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ###############</t>
-  </si>
-  <si>
-    <t>####0 ##0 #######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###############e##0</t>
-  </si>
-  <si>
-    <t>######## ######## ###############e#0</t>
-  </si>
-  <si>
-    <t>##### ######## ######## #### ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0.1 #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0.1 ##0</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ######## ######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ############# ##0</t>
-  </si>
-  <si>
-    <t>####0 ##0 ############# #0</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #0</t>
-  </si>
-  <si>
-    <t>####0##0###### #########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####e##0</t>
-  </si>
-  <si>
-    <t>####0##0 ####e#0</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######e#0</t>
-  </si>
-  <si>
-    <t>######## ######## ######e##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###########e##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###########e#0</t>
-  </si>
-  <si>
-    <t>####0##0 #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### ##0</t>
-  </si>
-  <si>
-    <t>##0##0#####e #######e #0</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #### #0</t>
-  </si>
-  <si>
-    <t>#0####0##0 #############e##0</t>
-  </si>
-  <si>
-    <t>#0####0##0 #############e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######## ;##### #####ddh</t>
-  </si>
-  <si>
-    <t>##0 ###### ######## ####0##0 ###### ###### ##0</t>
-  </si>
-  <si>
-    <t>##0 ###### ######## ####0##0 ###### ###### #0</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ############</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### ### ## ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0</t>
-  </si>
-  <si>
-    <t>###### ### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #0</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ######## ########e######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 #############</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ;#### #####ddh ##0</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ;#### #####ddh #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0.1e##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0.1e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ############</t>
-  </si>
-  <si>
-    <t>####0##0#########</t>
-  </si>
-  <si>
-    <t>####0##0 ##############e##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##############e#0</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ############e#0</t>
-  </si>
-  <si>
-    <t>####0##0e########## ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #######e##0</t>
-  </si>
-  <si>
-    <t>####0##0 #######e#0</t>
-  </si>
-  <si>
-    <t>####### ######## ####### ##0nn2 #0</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##0nn2 ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0</t>
-  </si>
-  <si>
-    <t>######## ######## #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0</t>
-  </si>
-  <si>
-    <t>####0##0##########e#0</t>
-  </si>
-  <si>
-    <t>####nn##nn######### #### ########</t>
-  </si>
-  <si>
-    <t>####0##0####### ##0</t>
-  </si>
-  <si>
-    <t>####0##0####### #0</t>
-  </si>
-  <si>
-    <t>####0##0######</t>
-  </si>
-  <si>
-    <t>####0##0######e##0</t>
-  </si>
-  <si>
-    <t>####0##0############# #0</t>
-  </si>
-  <si>
-    <t>####0##0############# ##0</t>
-  </si>
-  <si>
-    <t>####0##0#############e##0</t>
-  </si>
-  <si>
-    <t>####0##0#############e#0</t>
-  </si>
-  <si>
-    <t>####0##0######## ##### #### ######e #0</t>
-  </si>
-  <si>
-    <t>####0##0e##### ########</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##### ##</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##### #0</t>
-  </si>
-  <si>
-    <t>####0##0##############</t>
-  </si>
-  <si>
-    <t>######0############e##0</t>
-  </si>
-  <si>
-    <t>######0############e#0</t>
-  </si>
-  <si>
-    <t>####0##0 ######e#0 ##########e######</t>
-  </si>
-  <si>
-    <t>####0##0 ######e##0</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ########### ##0</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ########### #0</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ##0</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### #0</t>
-  </si>
-  <si>
-    <t>####0##0### #########</t>
-  </si>
-  <si>
-    <t>######## ######## ############## ##0</t>
-  </si>
-  <si>
-    <t>######## ######## ############## #0</t>
-  </si>
-  <si>
-    <t>##### ### ######## ### ######## ##0</t>
-  </si>
-  <si>
-    <t>##### ### ######## ### ######## #0</t>
-  </si>
-  <si>
-    <t>######## ######## ### ######## ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ### ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0##### ;### ########ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;####ddh ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;####ddh ;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ##### #####e #### #0</t>
-  </si>
-  <si>
-    <t>#### ##### ##### #### ##0</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ##01 ##0</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ##01 #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### y#### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### y#### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### y##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### y#0</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;######ddh ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;##0ddh</t>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHSHRAKL|SHRCH|KL|J~NADYAIBHTBBH|KL|THATHABHBBH SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHSHRAKL|SHRCH|KL|J~NADYAIBHTBBH|KL|THATHABHBBH SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>SHRATAN BHN AIBIVAVAS AIVADAMKAPI</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRADAK|BH|CH|K|CH|S|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBHCH SHRADAK|BH|CH|K|CH|S|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>P. P. DOTH (N)</t>
+  </si>
+  <si>
+    <t>P. P. DOTH (S)</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHBBHTHATHABHKL|SHRCH|KL|AIBHTBBH|KL|THATHABHKL|SHRCH|KL|AIBHTBBH SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHBBHTHATHABHKL|SHRCH|KL|AIBHTBBH|KL|THATHABHKL|SHRCH|KL|AIBHTBBH SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN LAMNATAPAJAMS LIVEM</t>
+  </si>
+  <si>
+    <t>BBH|DAPDAJ THAT|AI|T|K|S THAPDACH|K|BBH|CH|J S|CH|AI|DACH|J|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBH|DAPDAJ THAT|AI|T|K|S THAPDACH|K|BBH|CH|J S|CH|AI|DACH|J|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDACH|K|BBH|CH|J S|CH|AI|DACH|J|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDACH|K|BBH|CH|J S|CH|AI|DACH|J|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCHAPDACH|J|D|PDAM</t>
+  </si>
+  <si>
+    <t>CHN CHNJNATAJAPACHAMT CHAV.1</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRACH|J|SHR|CH|BBH|DAJ BBH|T|CHAN2MYABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRACH|J|SHR|CH|BBH|DAJ BBH|T|CH2Y|PKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH DYASHR|DAND YASHRACH|J|SHR|CH|BBH|DAJ|KKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|J~NADY|PKL|J~NADYAIBHT AIBHT|JBH|THABHKL|J~NADYACHKL|THATHABHKL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|J~NADY|PKL|J~NADYAIBHT AIBHT|JBH|THABHKL|J~NADYACHKL|THATHABHKL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|J~NADY|PKL|J~NADYAIBHT |PTHABHJTHATHABHKL|J~NADYACHKL|J~N</t>
+  </si>
+  <si>
+    <t>CHN CHN THANAKIPACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN PDAKAMNASAP SHRAMUPAD PDAKAMNASAP</t>
+  </si>
+  <si>
+    <t>CHN CHN |JATAMNAS</t>
+  </si>
+  <si>
+    <t>CHN CHN CHMKAMTAP</t>
+  </si>
+  <si>
+    <t>CHN CHN JMADAKANIMTAP</t>
+  </si>
+  <si>
+    <t>CHN CHN DANAIMTAMACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH THATHABHBBH SHRATHABHDYAK|CHJDYASHRADYAK AIBHTBBH|CHBBHDYASHRADYASHRCH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J AIBHT|J|CHAJBH|CHAJ|CH JBH|DAKMBBH|DAJ JBH|DAPT|JNDAM YADAKKBH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J AIBHT|J|CHAJBH|CHAJ|CH JBH|DAKMBBH|DAJ JBH|DAPT|JNDAM YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHK|D|J BBHCHABBHCH JBH|DAKMBBH|DAJ JBH|DAPT|JNDACH YADAKKBH</t>
+  </si>
+  <si>
+    <t>CHK|D|J BBHCHABBHCH JBH|DAKMBBH|DAJ JBH|DAPT|JNDACH YANBKKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJDYATHATHABHKL|AIBHT|KL|SHRCH|KL|J~NADYATHATHABH |PTHABHJTHATHABHDYABBHTHATHABHKL|AIBHT|KL|AIBHTBBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|CH|SHRAPCH|D YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|CH|SHRAPCH|D Y|PKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI |PCH|DAJ YADAKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI |PCH|DAJ YAK|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI |PCH|DAJ YANBKKBH</t>
+  </si>
+  <si>
+    <t>AIILAMUENADAKAMTAP THAMN TAN THAMASAJIMTAM TAVAMK</t>
+  </si>
+  <si>
+    <t>AIILAMUENADAKAMTAP THAMN TAN THAMASAJIMTAMTAVAMK</t>
+  </si>
+  <si>
+    <t>SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH |PKL|J~NADYASHRCH|KL|AIBHTBBHDYABBHTHATHABH SHRCH|KL|J~NAKL|BBH|SHRAKL|AIBHT|KL|THATHABHKL|J~NADYACH THATHABHSHRCH|KL|PTHABHJKL|J~NAKL|AIBHT SHRATHABHDYASHRAKLDYACHKLDYACHKL|J~NADYAJBH|THABHKL|J~N</t>
+  </si>
+  <si>
+    <t>AIBHT|JBH|THABHKL|J~NAKLDYACHKL|PTHABHJDYABBHJ~NADYAIBHT|KL|J~N AIBHT|KL|SHRAKL|J~NADYAIBHTBBH SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH THATHABHSHRCH|KL|PTHABHJKL|J~NAKL|AIBHT SHRATHABHDYASHRAKLDYACHKLDYACHKL|J~NADYAJBH|THABHKL|J~N |PKL|J~NADYASHRCH|KL|AIBHTBBHDYABBHTHATHABH SHRCH|KL|J~NAKL|BBH|SHRAKL|AIBHT|KL|THATHABHKL|J~NADYACH</t>
+  </si>
+  <si>
+    <t>THAMASAJIMTAM TAVAMK LAMDAKIP DAMAUVATAPAMS PDAJAMAT BVASASAMHAM</t>
+  </si>
+  <si>
+    <t>THAMASAJIMTAM TAVAMK JV.CCH PCHAJMT</t>
+  </si>
+  <si>
+    <t>COLLEG,BALLIA,NORTH P. P. SIAR NO-2 (E)</t>
+  </si>
+  <si>
+    <t>P. P. SIAR NO-2 (W)</t>
+  </si>
+  <si>
+    <t>P. P. SIAR NO-2 (M)</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDACH|CH|S|D YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDACH|CH|S|D Y|PKKBH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J|CH BBHCH BBHCH CHAPPDANYABBH|KKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN DAMRIUMSAPALAM</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|D|AI|SHRAPDAJ|DAPDAT|DAJ YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|D|AI|SHRAPDAJ|DAPDAT|DAJ YANBKKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYAJBH|THABHJ~NADYACHKL|AIBHTBBH|KL|THATHABHKL|AIBHT|KL|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT JBH|JBH|THABHKL|SHRADYABBH2 SDYAIBHT|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT|KL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYAJBH|THABHJ~NADYACHKL|AIBHTBBH|KL|THATHABHKL|AIBHT|KL|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT JBH|JBH|THABHKL|J~NADYAIBHT|KLDYACHKL|J~N SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYAJBH|THABHJ~NADYACHKL|AIBHTBBH|KL|THATHABHKL|AIBHT|KL|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT JBH|JBH|THABHKL|J~NADYAIBHT|KLDYACHKL|J~N SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>SMSAUMDAP NN DAN TAN BHMSAKAPATAMUCHANAT</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABHDYAJBH|JBH|THABHTHATHABH KL|BBHJ~NADYABBHTHATHABHKL|PKL|J~N SDYASHRATHABHDYAJBH|THABHJ~NADYACHKL|AIBHTBBH|KL|THATHABH AIBHT|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT|KL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJTHATHABHKL|J~NADYASHRCH|KL|PKL|J~N JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYAJBH|THABHJ~NADYACHKL|AIBHTBBH|KL|THATHABHKL|AIBHT|KL|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJTHATHABHKL|J~NADYASHRCH|KL|PKL|J~N JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYAJBH|THABHJ~NADYACHKL|AIBHTBBH|KL|THATHABHKL|AIBHT|KL|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH THATHABHBBH JBH|THABHK|PDYASHRCHADYABBHDYASHRADYAK|CHATHATHABHDYABBHDYASHR AIBHTBBH|CHK|D THATHABHDYAJDYABBH|CH1</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|D|J|DAMT YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|D|J|DAMT YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHCH|BBH|J|DACH|AI|CH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHCH|BBH|J|DACH|AI|CH YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHCH|BBH|J|DACH|AI|CH YAK|KKBH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J|CH BBHCH BBHCH BBHCH|BBH|J|DACH|AI|CH YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J|CH BBHCH BBHCH BBHCH|BBH|J|DACH|AI|CH Y|PKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN AIIMAICHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH |PPDAPBBH|CH|J DYABHPD YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH |PPDAPBBH|CH|J DYABHPD YANBKKBH</t>
+  </si>
+  <si>
+    <t>SHRATAN BHN AIBIVAVAS AIIMICHANAT |HIM</t>
+  </si>
+  <si>
+    <t>CHN CHN BIMA DAMIMTAMSAP NT IDAMNATAMIM</t>
+  </si>
+  <si>
+    <t>CHN CHN TMBIIMNASAP</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJDYAJ~NAKLDYACHKL|BBH|J~N DYACHJBH|THABHSHRAKL|J~NADYABBH|J~NADYACHKL|THATHABHKL|AIBHTBBH|KL|AIBHTBBH|KL|THATHABHKL|SHRCH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJDYAJ~NAKLDYACHKL|BBH|J~N DYACHJBH|THABHSHRAKL|J~NADYABBH|J~NADYACHKL|THATHABHKL|AIBHTBBH|KL|AIBHTBBH|KL|THATHABHKL|SHRCH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN JMADAKANAM CHMJAJAP CHIMTEMJAMT</t>
+  </si>
+  <si>
+    <t>CHN CHN THAMIIDAMNASAP DANAN JMASAUM</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHKL|J~NADYABBHTHATHABHKL|PTHABHJKL|J~NADYASHRATHABHDYABBHJ~NAKL THATHABHDYAJBH|JBH|THABHKL|J~NADYAIBHTBBH|KL|PKL|J~NADY|P SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHKL|J~NADYABBHTHATHABHKL|PTHABHJKL|J~NADYASHRATHABHDYABBHJ~NAKL THATHABHDYAJBH|JBH|THABHKL|J~NADYAIBHTBBH|KL|PKL|J~NADY|P SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|J~NADYAIBHTBBH|KL|THATHABHBBH SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|J~NADYAIBHTBBH|KL|THATHABHBBH SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN SMAIUMSAPALAM</t>
+  </si>
+  <si>
+    <t>THABHCH |PTHAPT|T|AI SHRCH|DAJMDAJ</t>
+  </si>
+  <si>
+    <t>CHN CHN DAVASADAMCHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JDANBBH|CH|J SHRCH|DAK|CH|K|BH|T|S|DAK</t>
+  </si>
+  <si>
+    <t>LIMDAKAP NN DAN TAN TMUCHANAT BIMDAKAMASAM</t>
+  </si>
+  <si>
+    <t>SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH |PBBHJ~NADYASHRCH|KL|AIBHTBBH|KL|THATHABH THATHABHDYATHATHABH SHRCH|KL|THATHABH AIBHT|KL|THATHABH AIBHT|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|J~NAKLDYACHKL|J~N</t>
+  </si>
+  <si>
+    <t>SDYASHRCH|KL|SHRCH|SHRCH|JBH|THABH |PBBHJ~NADYASHRCH|KL|AIBHTBBH|KL|THATHABH THATHABHDYATHATHABH SHRCH AIBHT|KL|THATHABH AIBHT|J~NADYABBH|JBH|JBH|THABHKL|THATHABHKL|AIBHT SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|J~NAKLDYACHKL|J~N SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>P. P. KARNI (E)</t>
+  </si>
+  <si>
+    <t>P. P. KARNI (W)</t>
+  </si>
+  <si>
+    <t>CHN CHN AIMKAKAVACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN TMRACHANAT CHAMU THANAPASAKAPADAH</t>
+  </si>
+  <si>
+    <t>CHN CHN TMRACHANAT VSAK THANAPASAKAPADAH</t>
+  </si>
+  <si>
+    <t>CHN CHN AIMUENAKAKAPADACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN CHMEINIMTAP</t>
+  </si>
+  <si>
+    <t>KMATAMR PDAJAMAT BVASASAMHAM CHMENIMTAP</t>
+  </si>
+  <si>
+    <t>CHN CHN CHMIMTACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHDAI|CH|S|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHDAI|CH|S|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHPDAJMDASHR|DAJ YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHPDAJMDASHR|DAJ Y|PKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHPDAJMDASHR|DAJ YAK|KKBH</t>
+  </si>
+  <si>
+    <t>CHMDABIMLAMJ THIMUMD CHIMTEMJAMT</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J|CH BBHCH BBHCH DYANDAS|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J|CH BBHCH BBHCH DYANDAS|D YAK|KKBH</t>
+  </si>
+  <si>
+    <t>E. P. P. AWAYA (M)</t>
+  </si>
+  <si>
+    <t>E. P. P. AWAYA (W)</t>
+  </si>
+  <si>
+    <t>AIMKIMD AIMIAMTAP AIMUPAJAP THINUMTAP</t>
+  </si>
+  <si>
+    <t>CHN CHN DAPEITAMNASAP</t>
+  </si>
+  <si>
+    <t>THATHABHKDYACHKL|J~NADYABBH|THATHABHKL|J~NADYATHATHABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|THATHABHKL|SHRCH|KL|AIBHTBBH|KL|J~NADYATHATHABHKLDYACH JBH|JBH|THABHKL|THATHABHKL|PKL|J~NADYABBH|J~NADY|PTHABHJ J~NASDYACHKL|THATHABH SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>THATHABHKDYACHKL|J~NADYABBH|THATHABHKL|J~NADYATHATHABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|THATHABHKL|SHRCH|KL|AIBHTBBH|KL|J~NADYATHATHABHKLDYACH JBH|JBH|THABHKL|THATHABHKL|PKL|J~NADYABBH|J~NADY|PTHABHJ J~NASDYACHKL|THATHABH SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHBBHJ~NADYAIBHTBBH|KL|J~NADYATHATHABHKL|AIBHT|KL|J~N |PTHABHJDYAJ~NADYAIBHT|KL|SHRATHABHDYABBHBBHJ~NADYAJBH|JBH|THABHKL|J~NADYAIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHBBHJ~NADYAIBHTBBH|KL|J~NADYATHATHABHKL|AIBHT|KL|J~N |PTHABHJDYAJ~NADYAIBHT|KL|SHRATHABHDYABBHBBHJ~NADYAJBH|JBH|THABHKL|J~NADYAIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|CHAMPDAPD PPDAJ</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHDASHR|K|DAJ|CH SHRCH|CH|J|SHR|CH|BBH|CH|J YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHDASHR|K|DAJ|CH SHRCH|CH|J|SHR|CH|BBH|CH|J Y|PKKBH</t>
+  </si>
+  <si>
+    <t>P. P. AKHOP (W)</t>
+  </si>
+  <si>
+    <t>SHRATAN BHN AIBIVAVAS |AIVACH</t>
+  </si>
+  <si>
+    <t>KMAMADAKATAM KPAHATAP BVASASAMHAM THAMASAJIMTAMTAVAMK</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHJ~NADYAK|SHRCH|KL|J~N AIBHT|JBH|THABHKL|J~NADYABBHJ~NADYAIBHTBBH|KL|THATHABHKL|AIBHT|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHJ~NADYAK|SHRCH|KL|J~N AIBHT|JBH|THABHKL|J~NADYABBHJ~NADYAIBHTBBH|KL|THATHABHKL|AIBHT|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN THAMDAMTAM AIMPALAMK THANAIMTAM</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PKL|SHRAKL|THATHABHKL|SHRCH|KL|AIBHTBBH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT AIBHTBBHDYATHATHABHKL|JBH|THABHKL|J~NADYATHATHABHKLDYACHKL|THATHABH SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PKL|SHRAKL|THATHABHKL|SHRCH|KL|AIBHTBBH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT AIBHTBBHDYATHATHABHKL|JBH|THABHKL|J~NADYATHATHABHKLDYACHKL|THATHABH SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN AINAUIM</t>
+  </si>
+  <si>
+    <t>CHN CHN DAMSAMATAM</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI |PDAJ|S|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI |PDAJ|S|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN DAMUCHANAT DAMIKAMAM</t>
+  </si>
+  <si>
+    <t>CHN CHN AIMAUMTAP</t>
+  </si>
+  <si>
+    <t>CHN CHN LAMRAPALAMCHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCHAPCH|K|SHR|D</t>
+  </si>
+  <si>
+    <t>CHN CHN THAMIVATAM</t>
+  </si>
+  <si>
+    <t>CHN CHN AIIPANATAP CHTAMAUTAMRAM</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH CHPJ|DAPCH|N BBH|DASHR|SHR|CH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH CHPJ|DAPCH|NBBH|DASHR|SHR|CH YANBKKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH J~NASDYAK|J~NADYAIBHTBBH|KL|THATHABHKL|PKL|J~N SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH J~NASDYAK|J~NADYAIBHTBBH|KL|THATHABHKL|PKL|J~N SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN THIPADAK SMAIMDEPADIM</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRCH|KL|THATHABHDYABBHJ~NADYABBH|J~NADYAIBHTBBH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH SHRCH|KL|THATHABHDYABBHJ~NADYABBH|J~NADYAIBHTBBH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|CH|THAPDAPDAJ|D</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|THATHABHDYAK|BBHBBHJ~N AIBHT|J~NADYAK|THATHABHKL|AIBHTBBH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|THATHABHDYAK|BBHBBHJ~N AIBHT|J~NADYAK|THATHABHKL|AIBHTBBH|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN AIPAKIMNASAP</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH |PPDAPBBH|CH|J SHRACH|SHR|CHPD YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH |PPDAPBBH|CH|J SHRACH|SHR|CHPD Y|PKKBH</t>
+  </si>
+  <si>
+    <t>SHRATAN BHN AIBIVAVAS AIIMICHANAT JPAJAPIM</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH K|DAPDAJ|CH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH K|DAPDAJ|CH YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN THAMTADAMH THAMEMDAJACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN AIMPAKACHANATAM</t>
+  </si>
+  <si>
+    <t>CHN CHN BIMAIMIEMCHANAT</t>
+  </si>
+  <si>
+    <t>CHNATA DAMKIMLAUPA TANETHAMTAMNASAP</t>
+  </si>
+  <si>
+    <t>CHN CHN THAMTAMNASAP</t>
+  </si>
+  <si>
+    <t>CHN CHN JPATADAMP DAMNASAMTAMP</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH CHAMD|DAJ S|DAT|CH|S|DABBH|CH|J YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH CHAMD|DAJ S|DAT|CH|S|DABBH|CH|J YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN BHNATAMINUM</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH J~NASDYATHATHABHKL|AIBHT|KL|J~NADYATHATHABHKL|PTHABHJTHATHABHDYABBHTHATHABHKL|AIBHT|KL|AIBHTBBH SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH J~NASDYATHATHABHKL|AIBHT|KL|J~NADYATHATHABH |PTHABHJTHATHABHDYABBHTHATHABHKL|AIBHT|KL|AIBHTBBH SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBH|CH|BH|DAPCHAND YADAKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN THATAMIPAUCHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH DYANDAJ|DACH|DAI|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH DYANDAJ|DACH SHRCH|DAI|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH DYANDAJ|DACH SHRCH|DAI|D BBH|T|CH1</t>
+  </si>
+  <si>
+    <t>CHN CHN DAMITAMRACHANAT</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHKL|J~NADYAIBHT|KL|J~NADYAIBHTBBH|KL|THATHABHBBH DYACHJ~NADYABBH|J~NADYATHATHABH JBH|JBH|THABHJ~NADY|PTHABHJKL|PTHABHJKL|THATHABH SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|JBH|THABHKL|J~NADYAIBHT|KL|J~NADYAIBHTBBH|KL|THATHABHBBH DYACHJ~NADYABBH|J~NADYATHATHABH JBH|JBH|THABHJ~NADY|PTHABHJKL|PTHABHJKL|THATHABH SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|DAJ|DACH|THAP YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|DAJ|DACH|THAP Y|PKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN TMUMCHAMJAJAP JMECHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHN THAMIMTACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN CHAMUMKAM</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|DAJND JDASHR|SHR|CH BBHDASHR|SHR|CH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|DAJND JDASHR|SHR|CH BBHDASHR|SHR|CH YAK|KKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN THIPAUCHANATAM CHAVAN.1</t>
+  </si>
+  <si>
+    <t>SHRATAN BHN AIBIVAVAS THIPAUCHANATAM CHAVAN.1</t>
+  </si>
+  <si>
+    <t>CHN CHN THAMIIDAMNASAP</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|CHAMPPD JBH|J|DAPNDAK</t>
+  </si>
+  <si>
+    <t>CHN CHN SHRAMRAMNASAP</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|CH|J|CHPDAJ|DABBH|CH|J</t>
+  </si>
+  <si>
+    <t>CHN CHN AIMJANIMTAP</t>
+  </si>
+  <si>
+    <t>CHN CHN THAPAIPACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN THAMTAMUM DANAISAPECHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN |UMUM</t>
+  </si>
+  <si>
+    <t>CHN CHN AIVAKIMDACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN DAMRIMNUM</t>
+  </si>
+  <si>
+    <t>CHN CHN CHMDABIUM</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH THATHABHDYAIBHTBBHDYABBHJ~NADYAIBHT|KL|J~NADYASHRCH SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH THATHABHDYAIBHTBBHDYABBHJ~NADYAIBHT|KL|J~NADYASHRCH SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH DYACHSHRADYABBHJ~NADY|PTHABHJKL|J~N JBH|JBH|THABHJ~NADYASHRCH|KL|SHRATHABHDYABBHAIBHTBBH|KL|J~NADYATHATHABHKL|AIBHT|KL|J~N SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH DYACHSHRADYABBHJ~NADY|PTHABHJKL|J~N JBH|JBH|THABHJ~NADYASHRCH|KL|SHRATHABHDYABBHAIBHTBBH|KL|J~NADYATHATHABHKL|AIBHT|KL|J~N SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBHPCH|T|DACH|K|CH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBHPCH|T|DACH|K|CH YANBKKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHTHATHABHK|PKL|J~NADYASHRCH|KL|AIBHTBBH|KL|J~NADYACHKL|J~N SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHTHATHABHK|PKL|J~NADYASHRCH|KL|AIBHTBBH|KL|J~NADYACHKL|J~N SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN SHRAMUPAD AIPELAMDAK</t>
+  </si>
+  <si>
+    <t>CHN CHN KMISACHANATAM</t>
+  </si>
+  <si>
+    <t>CHN CHN THMTIMKAM NT ICHNATAM</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI S|DACH|J|D SHRCHAPDAM YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI S|DACH|J|D SHRCHAPDAM Y|PKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDAJ|DACHAND YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDAJ|DACHAND YANBKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI THAPDAJ|DACHAND YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI THAPDAJ|DACHAND YAK|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|J|CH THABHCH |PTHAPT|T|AI THAPDAJ|DACHAND Y|PKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN BIIPAJAPAPALAM</t>
+  </si>
+  <si>
+    <t>P. P. PATOI (E)</t>
+  </si>
+  <si>
+    <t>CHN CHN TAPAHAMI SHRAMUPAD TAPAHAMI</t>
+  </si>
+  <si>
+    <t>CHN CHN TMNEMTAM</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J BBHCH BBHCH SHRACH|J|K|DACH SHRCHAPCH|T|CH|J|BBH|CH|J YADAKKBH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J BBHCH BBHCH SHRACH|J|K|DACH SHRCHAPCH|T|CH|J|BBH|CH|J YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRACH|J|K|DACH SHRCHAPCH|T|CH|J|BBH|CH|J YATHABHDAJ|CH|T|DAK JBH|DAMSHR|CH|KKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN SHRAMUNAMVADAIMUCHANAT CHAMIMT AIMTAMA</t>
+  </si>
+  <si>
+    <t>SHRCH|D BBHDAMTHAPCH|N SHRCH|DAK|S|D YANBKKBH BBHCH BBHCH AIBHT|DANCH|DAT|K SHRCHAPDANBBH|CH|J</t>
+  </si>
+  <si>
+    <t>CHN CHN SHRAMUNAMUAIMUCHANAT CHAMIMT AM</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABHKL|AIBHT|KL|J~NADYABBH JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBHDYABBH|J~N SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBHDYABBH|J~N SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHJ~NADYASHRCH|KL|SHRATHABHDYABBHJ~NADY|PKL|J~NADY|PTHABHJ AIBHT|JBH|THABHBBHJ~NADYABBH|J~NADYASHRCH |PTHABHJTHATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBHDYABBH|J~N</t>
+  </si>
+  <si>
+    <t>THATHABHBBH THATHABHBBH AIBHTBBHDYAK|SHRADYAK|BBHDYASHRCHADYABBH</t>
+  </si>
+  <si>
+    <t>CHN CHN |MTAPACHANAT AIMTALAM</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHTHATHABHKL|J~NADYASHRCH|KL|AIBHTBBH|KL|J~NADYAIBHT|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH KL|BBHTHATHABHKL|J~NADYASHRCH|KL|AIBHTBBH|KL|J~NADYAIBHT|KL|JBH|JBH|THABHKL|THATHABHKL|AIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABHKL|AIBHT|KL SHRCH|KL|J~NADYAIBHTBBH|KL|PKL|J~NADYABBH|THATHABHKL AIBHT|KL|THATHABHKL|AIBHTBBH|KL|PKL|J~NADYACHKL|J~NADY|P |PTHABHJTHATHABHKL|J~NADYACHBBH|J~NADYAIBHT|KL|THATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHN|IPATAMNASAP DANAN BIMTAMNUMVAD</t>
+  </si>
+  <si>
+    <t>CHN CHN AIIPANATAM LAVACHAMSACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH |PPCHPT|J|CH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH |PPCHPT|J|CH YANBKKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|J~NADYAK|J~NADYATHATHABHKL|SHRCH|KL|AIBHTBBH|KL|J~NADYAIBHT SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|J~NADYAK|J~NADYATHATHABHKL|SHRCH|KL|AIBHTBBH|KL|J~NADYAIBHT SDYASHRCH|KL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|J~NADYAK|J~NADYATHATHABHKL|SHRCH|KL|AIBHTBBH|KL|J~NADYAIBHT SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN JTAPASAVA DAMDAKAM</t>
+  </si>
+  <si>
+    <t>CHN CHN KMUMSAMAMAT</t>
+  </si>
+  <si>
+    <t>CHN CHN |IMECHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JCH|BBHNDAJ JBHPDABHNDAK|BBH|CH|J YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JCH|BBHNDAJ JBHPDABHNDAK|BBH|CH|J YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN KPASAUMD DAMKANAPACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH AIDAPDAMDAK|CH YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH AIDAPDAMDAK|CH Y|PKKBH</t>
+  </si>
+  <si>
+    <t>SHRCH|DAK|S|D BBHCH BBHCH AIDAPDAMDAK|CH YAK|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHDAJMCH|D JCH|BBH|BBH|CH|J YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBHDAJMCH|D JCH|BBH|BBH|CH|J Y|PKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN DANIUMKACHANAT SHRAMCHAJAP DAMCHIP</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH S|DACHANDABBH|DAJ YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH S|DACHANDABBH|DAJ YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN AINARAMDAMCHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBHPCH|NBBH|CH|J|D BBH|T|CHAN2 YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN AINACHACHAMCHAMSAP</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|CHMDAJ|CH PYABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|CHMDAJ|CH PY|PKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN AIPAMTAMIMJAM</t>
+  </si>
+  <si>
+    <t>CHN CHN DAMDENATAPALAM</t>
+  </si>
+  <si>
+    <t>CHN CHN DAMSAPACHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN THAPENADACHANAT KMDAKAM</t>
+  </si>
+  <si>
+    <t>CHN CHN CHMTAMETAM SHRANATAMD</t>
+  </si>
+  <si>
+    <t>CHN CHN CHAMDAMNATAM</t>
+  </si>
+  <si>
+    <t>CHN CHN |IPATAMNASAP</t>
+  </si>
+  <si>
+    <t>CHN CHN BHMIEMCHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN THIVARAMNACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|CHPJ|D THABHDAJ|BBH|CH|J YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH JBH|CHPJ|D THABHDAJ|BBH|CH|J Y|PKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRACH|SHR|AI|DACH|CH|S|D CHAJ PSHRCH|CHMPT|J|BH|DAK|T</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|DAJ|CH|NBBH|CH|J</t>
+  </si>
+  <si>
+    <t>CHN CHN BIIPAJAMNADAM</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|DANJ|DACH|AI|CH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|DANJ|DACH|AI|CH YANBKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN THAPEINADACHANATAM</t>
+  </si>
+  <si>
+    <t>CHN CHN JNATAP KMNASAMJACHANAT</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH THATHABHSHRCH|KL|AIBHTBBH|KL|J~NADYATHATHABHKLDYACHKL|THATHABH SHRCH|KL|J~NADYACHKL|J~NADYATHATHABHKLDYACHKL|THATHABH SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH THATHABHSHRCH|KL|AIBHTBBH|KL|J~NADYATHATHABHKLDYACHKL|THATHABH SHRCH|KL|J~NADYACHKL|J~NADYATHATHABHKLDYACHKL|THATHABH SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHN CHN TMDAMNACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH THATHABHBBH AIBHTBBHDYAJDYASHRCH|CHK AIDYAK|PDYABBHDYACH THATHABHK|AIBHTDYAIBHTDYABBH BBH|SHR CHSHRATHABHCHK|BBHDYATHATHABHDYABBHDYASHR</t>
+  </si>
+  <si>
+    <t>SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH |PTHABHJTHATHABHKL|SHRAKL|AIBHTBBHDYABBHJ~N |PKL|J~NADYACHKL|THATHABHKL|BBH JBH|JBH|THABHJ~NADY|PTHABHJKL|PTHABHJKL|THATHABH THATHABHDYAIBHT BBHAIBHT|JBH|THABHBBHJ~NADYATHATHABHKL|JBH|JBH|THABHKL|THATHABHKL|AIBHT</t>
+  </si>
+  <si>
+    <t>Y|PKKBH BBHCH BBHCH |PDAJ|S|D S|CH|AI|DAP JDACH</t>
+  </si>
+  <si>
+    <t>AIMKIMD AIMIAMTAP AIMUPAJAP BHMRAPALAM</t>
+  </si>
+  <si>
+    <t>TMUCHANAT CHN CHN BIMDAKAP AIMTAMP AIMUIIMS</t>
+  </si>
+  <si>
+    <t>CHN CHN SHRAMAJIUMT LMANAICHANAT</t>
+  </si>
+  <si>
+    <t>CHN CHN PDAMUPACHANAT</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHJ~NADYACHKL|SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|AIBHT|KL|J~NADYABBHJ~N SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHJ~NADYACHKL|SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|AIBHT|KL|J~NADYABBHJ~N SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBH|CH|DAMCH YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBH|CH|DAMCH YAK|KKBH</t>
+  </si>
+  <si>
+    <t>AINAIME PDAJAMAT BVASASAMHAM JMTAPAIMTAM LAMVAD</t>
+  </si>
+  <si>
+    <t>SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH AIBHT|KL|J~NAKL|J~NAKL|AIBHT SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|AIBHT|KL|J~NADYABBHJ~N</t>
+  </si>
+  <si>
+    <t>CHN CHN |IMKANASACHANAT DAMKAMTAP</t>
+  </si>
+  <si>
+    <t>LAMDAKIP DAMIMAPAKALAMSAMLAM DAMSAMCH</t>
+  </si>
+  <si>
+    <t>BHMTEMADACHANAT LAMDAKIP DAMIMAPAKALAMSAMLAM DAMSAMCH</t>
+  </si>
+  <si>
+    <t>THABHDAJMD|K|BBH|CH|J BBHCH BBHCH K|DAI|DABBH THABHDAJMD|K|BBH|CH|J YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH K|DAI|DABBH THABHDAJMD|K|BBH|CH|J YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCHAPDABBH|DASHR|DAPCH YAK|DAI|DABBH THABHDAJMD|K|BBH|CH|J|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDATHAPDAS|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH THAPDATHAPDAS|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH AIBHT|DAPDAK|BH|CH|J|D YABBH|DABH|DAJ|DAKKBH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH AIBHT|DAPDAK|BH|CH|J|D YABBH|DABH|DAJ|DAKKBH YANBKKBH</t>
+  </si>
+  <si>
+    <t>SHRAMDAJAM PDAJAMAT BVASASAMHAM CHAMHAMTAM</t>
+  </si>
+  <si>
+    <t>CHN CHN JPASAMTAP CHAMHAMTAM</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|T|SHRAPCH|S|D YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|T|SHRAPCH|S|D YANBKKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHJ~NADYAIBHTBBH|KL|J~NADYAIBHT|KL|THATHABH SDYAJ~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH JBH|JBH|THABHJ~NADYAIBHTBBH|KL|J~NADYAIBHT|KL|THATHABH SDYABBH|JBH|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>SHRCH|DAK|S|D BBHCH BBHCH BBHDAJMCH|J|DANBBH|CH|J</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCH|D|DAJ|CH</t>
+  </si>
+  <si>
+    <t>CHN CHN THIPAJANADAM</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH S|T|SHRAPDAND YABBH|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH S|T|SHRAPDAND YAK|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH |PD|NDAJ|CH Y S|T|SHRAPDANDAKKBH Y|PKKBH</t>
+  </si>
+  <si>
+    <t>CHN CHN KIMAUMTAP</t>
+  </si>
+  <si>
+    <t>CHN CHN KMAVATAPALAM</t>
+  </si>
+  <si>
+    <t>CHN CHN CHAMTAMIP CHAVAN2</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBH|DAJ|DAPCH YADAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBH|DAJ|DAPCH YAK|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH BBH|DAMJ|DAPCH YANBKKBH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH THATHABHSHRCH|KL|AIBHTBBH|KL|J~NADYAK|SHR SDYAJBH|JBH|THABHKL|SHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>JBH|JBH|THABHTHATHABH JBH|JBH|THABHTHATHABH THATHABHSHRCH|KL|AIBHTBBH|KL|J~NADYAK|SHR SKL|BBHSHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>BBHCH BBHCH SHRCHAPDAI|CHMBBH|CH|J</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>CHN CHN KPIUM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -890,8 +1358,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -907,7 +1383,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -915,12 +1391,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,88 +1713,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>266</v>
+        <v>422</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
-        <v>268</v>
+        <v>424</v>
       </c>
       <c r="F2" t="s">
-        <v>269</v>
+        <v>425</v>
       </c>
       <c r="G2" t="s">
-        <v>270</v>
+        <v>426</v>
       </c>
       <c r="H2" t="s">
-        <v>271</v>
+        <v>427</v>
       </c>
       <c r="I2" t="s">
-        <v>272</v>
+        <v>428</v>
       </c>
       <c r="J2" t="s">
-        <v>273</v>
+        <v>429</v>
       </c>
       <c r="K2" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
       <c r="L2" t="s">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="M2" t="s">
-        <v>276</v>
+        <v>432</v>
       </c>
       <c r="N2" t="s">
-        <v>277</v>
+        <v>433</v>
       </c>
       <c r="O2" t="s">
-        <v>278</v>
+        <v>434</v>
       </c>
       <c r="P2" t="s">
-        <v>279</v>
+        <v>435</v>
       </c>
       <c r="Q2" t="s">
-        <v>280</v>
+        <v>436</v>
       </c>
       <c r="R2" t="s">
-        <v>281</v>
+        <v>437</v>
       </c>
       <c r="S2" t="s">
-        <v>282</v>
+        <v>438</v>
       </c>
       <c r="T2" t="s">
-        <v>283</v>
+        <v>439</v>
       </c>
       <c r="U2" t="s">
-        <v>284</v>
+        <v>440</v>
       </c>
       <c r="V2" t="s">
-        <v>285</v>
+        <v>441</v>
       </c>
       <c r="W2" t="s">
-        <v>286</v>
+        <v>442</v>
       </c>
       <c r="X2" t="s">
-        <v>287</v>
+        <v>443</v>
       </c>
       <c r="Y2" t="s">
-        <v>288</v>
+        <v>444</v>
       </c>
       <c r="Z2" t="s">
-        <v>289</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1308,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>961</v>
@@ -1388,7 +1957,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>1088</v>
@@ -1468,7 +2037,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>634</v>
@@ -1548,7 +2117,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>621</v>
@@ -1628,7 +2197,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>870</v>
@@ -1708,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>633</v>
@@ -1788,7 +2357,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>702</v>
@@ -1868,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>702</v>
@@ -1948,7 +2517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>897</v>
@@ -2028,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>943</v>
@@ -2108,7 +2677,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>1054</v>
@@ -2188,7 +2757,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>830</v>
@@ -2268,7 +2837,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>819</v>
@@ -2348,7 +2917,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>1050</v>
@@ -2428,7 +2997,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>974</v>
@@ -2508,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>920</v>
@@ -2588,7 +3157,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>1077</v>
@@ -2668,7 +3237,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>697</v>
@@ -2748,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>598</v>
@@ -2828,7 +3397,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>573</v>
@@ -2908,7 +3477,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>446</v>
@@ -2988,7 +3557,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>1013</v>
@@ -3068,7 +3637,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>700</v>
@@ -3148,7 +3717,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>879</v>
@@ -3228,7 +3797,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>1035</v>
@@ -3308,7 +3877,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>1092</v>
@@ -3388,7 +3957,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>723</v>
@@ -3468,7 +4037,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>769</v>
@@ -3548,7 +4117,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>868</v>
@@ -3628,7 +4197,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>603</v>
@@ -3708,7 +4277,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>686</v>
@@ -3788,7 +4357,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>762</v>
@@ -3868,7 +4437,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>635</v>
@@ -3948,7 +4517,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>676</v>
@@ -4028,7 +4597,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>675</v>
@@ -4108,7 +4677,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C38">
         <v>587</v>
@@ -4188,7 +4757,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>634</v>
@@ -4268,7 +4837,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>545</v>
@@ -4348,7 +4917,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>995</v>
@@ -4428,7 +4997,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>862</v>
@@ -4508,7 +5077,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>922</v>
@@ -4588,7 +5157,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>824</v>
@@ -4668,7 +5237,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>699</v>
@@ -4748,7 +5317,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>672</v>
@@ -4828,7 +5397,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>923</v>
@@ -4908,7 +5477,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>868</v>
@@ -4988,7 +5557,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>471</v>
@@ -5068,7 +5637,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>1105</v>
@@ -5148,7 +5717,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>1022</v>
@@ -5228,7 +5797,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>1123</v>
@@ -5308,7 +5877,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>1117</v>
@@ -5388,7 +5957,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>1044</v>
@@ -5468,7 +6037,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>864</v>
@@ -5548,7 +6117,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>895</v>
@@ -5628,7 +6197,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>869</v>
@@ -5708,7 +6277,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>1038</v>
@@ -5788,7 +6357,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>1037</v>
@@ -5868,7 +6437,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>1055</v>
@@ -5948,7 +6517,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>1067</v>
@@ -6028,7 +6597,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>1051</v>
@@ -6108,7 +6677,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>1032</v>
@@ -6188,7 +6757,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>1044</v>
@@ -6268,7 +6837,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>997</v>
@@ -6348,7 +6917,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>1030</v>
@@ -6428,7 +6997,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>1067</v>
@@ -6508,7 +7077,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>1155</v>
@@ -6588,7 +7157,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>716</v>
@@ -6668,7 +7237,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>1111</v>
@@ -6748,7 +7317,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>1116</v>
@@ -6828,7 +7397,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>1041</v>
@@ -6908,7 +7477,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>910</v>
@@ -6988,7 +7557,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>636</v>
@@ -7068,7 +7637,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>811</v>
@@ -7148,7 +7717,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>414</v>
@@ -7228,7 +7797,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>1067</v>
@@ -7308,7 +7877,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>761</v>
@@ -7388,7 +7957,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>541</v>
@@ -7468,7 +8037,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>790</v>
@@ -7548,7 +8117,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>845</v>
@@ -7628,7 +8197,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>1089</v>
@@ -7708,7 +8277,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>671</v>
@@ -7788,7 +8357,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>904</v>
@@ -7868,7 +8437,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>878</v>
@@ -7948,7 +8517,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>1031</v>
@@ -8028,7 +8597,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>980</v>
@@ -8108,7 +8677,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>959</v>
@@ -8188,7 +8757,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>1154</v>
@@ -8268,7 +8837,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>858</v>
@@ -8348,7 +8917,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>887</v>
@@ -8428,7 +8997,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>894</v>
@@ -8508,7 +9077,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>502</v>
@@ -8588,7 +9157,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="C94">
         <v>1037</v>
@@ -8668,7 +9237,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>1092</v>
@@ -8748,7 +9317,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>840</v>
@@ -8828,7 +9397,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="C97">
         <v>790</v>
@@ -8908,7 +9477,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>737</v>
@@ -8988,7 +9557,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>1056</v>
@@ -9068,7 +9637,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>1009</v>
@@ -9148,7 +9717,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="C101">
         <v>993</v>
@@ -9228,7 +9797,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>780</v>
@@ -9308,7 +9877,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>918</v>
@@ -9388,7 +9957,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>622</v>
@@ -9468,7 +10037,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>607</v>
@@ -9548,7 +10117,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>1077</v>
@@ -9628,7 +10197,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>1083</v>
@@ -9708,7 +10277,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>936</v>
@@ -9788,7 +10357,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>958</v>
@@ -9868,7 +10437,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>365</v>
@@ -9948,7 +10517,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>775</v>
@@ -10028,7 +10597,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>732</v>
@@ -10108,7 +10677,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>859</v>
@@ -10188,7 +10757,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>1007</v>
@@ -10268,7 +10837,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>1122</v>
@@ -10348,7 +10917,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>670</v>
@@ -10428,7 +10997,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>725</v>
@@ -10508,7 +11077,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>884</v>
@@ -10588,7 +11157,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="C119">
         <v>993</v>
@@ -10668,7 +11237,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="C120">
         <v>834</v>
@@ -10748,7 +11317,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="C121">
         <v>549</v>
@@ -10828,7 +11397,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>1022</v>
@@ -10908,7 +11477,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>598</v>
@@ -10988,7 +11557,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>591</v>
@@ -11068,7 +11637,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>600</v>
@@ -11148,7 +11717,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="C126">
         <v>1139</v>
@@ -11228,7 +11797,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="C127">
         <v>722</v>
@@ -11308,7 +11877,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="C128">
         <v>680</v>
@@ -11388,7 +11957,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="C129">
         <v>906</v>
@@ -11468,7 +12037,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="C130">
         <v>790</v>
@@ -11548,7 +12117,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="C131">
         <v>701</v>
@@ -11628,7 +12197,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="C132">
         <v>1144</v>
@@ -11708,7 +12277,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="C133">
         <v>949</v>
@@ -11788,7 +12357,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="C134">
         <v>1013</v>
@@ -11868,7 +12437,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="C135">
         <v>1006</v>
@@ -11948,7 +12517,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="C136">
         <v>744</v>
@@ -12028,7 +12597,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="C137">
         <v>727</v>
@@ -12108,7 +12677,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="C138">
         <v>1176</v>
@@ -12188,7 +12757,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="C139">
         <v>1146</v>
@@ -12268,7 +12837,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="C140">
         <v>957</v>
@@ -12348,7 +12917,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="C141">
         <v>1097</v>
@@ -12428,7 +12997,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="C142">
         <v>587</v>
@@ -12508,7 +13077,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="C143">
         <v>652</v>
@@ -12588,7 +13157,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>86</v>
+        <v>163</v>
       </c>
       <c r="C144">
         <v>785</v>
@@ -12668,7 +13237,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="C145">
         <v>1065</v>
@@ -12748,7 +13317,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
       <c r="C146">
         <v>970</v>
@@ -12828,7 +13397,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="C147">
         <v>997</v>
@@ -12908,7 +13477,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>1109</v>
@@ -12988,7 +13557,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>880</v>
@@ -13068,7 +13637,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="C150">
         <v>578</v>
@@ -13148,7 +13717,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="C151">
         <v>939</v>
@@ -13228,7 +13797,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="C152">
         <v>658</v>
@@ -13308,7 +13877,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="C153">
         <v>821</v>
@@ -13388,7 +13957,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="C154">
         <v>811</v>
@@ -13468,7 +14037,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>43</v>
+        <v>173</v>
       </c>
       <c r="C155">
         <v>803</v>
@@ -13548,7 +14117,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="C156">
         <v>955</v>
@@ -13628,7 +14197,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="C157">
         <v>1101</v>
@@ -13708,7 +14277,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="C158">
         <v>976</v>
@@ -13788,7 +14357,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="C159">
         <v>994</v>
@@ -13868,7 +14437,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="C160">
         <v>945</v>
@@ -13948,7 +14517,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="C161">
         <v>594</v>
@@ -14028,7 +14597,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="C162">
         <v>596</v>
@@ -14108,7 +14677,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="C163">
         <v>922</v>
@@ -14188,7 +14757,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="C164">
         <v>525</v>
@@ -14268,7 +14837,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="C165">
         <v>377</v>
@@ -14348,7 +14917,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="C166">
         <v>1063</v>
@@ -14428,7 +14997,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="C167">
         <v>1182</v>
@@ -14508,7 +15077,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="C168">
         <v>904</v>
@@ -14588,7 +15157,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>122</v>
+        <v>186</v>
       </c>
       <c r="C169">
         <v>789</v>
@@ -14668,7 +15237,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="C170">
         <v>595</v>
@@ -14748,7 +15317,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="C171">
         <v>660</v>
@@ -14828,7 +15397,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="C172">
         <v>632</v>
@@ -14908,7 +15477,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="C173">
         <v>837</v>
@@ -14988,7 +15557,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>41</v>
+        <v>191</v>
       </c>
       <c r="C174">
         <v>913</v>
@@ -15068,7 +15637,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C175">
         <v>747</v>
@@ -15148,7 +15717,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="C176">
         <v>572</v>
@@ -15228,7 +15797,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="C177">
         <v>1114</v>
@@ -15308,7 +15877,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="C178">
         <v>679</v>
@@ -15388,7 +15957,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="C179">
         <v>715</v>
@@ -15468,7 +16037,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="C180">
         <v>1137</v>
@@ -15548,7 +16117,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="C181">
         <v>1077</v>
@@ -15628,7 +16197,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="C182">
         <v>786</v>
@@ -15708,7 +16277,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="C183">
         <v>598</v>
@@ -15788,7 +16357,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="C184">
         <v>623</v>
@@ -15868,7 +16437,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="C185">
         <v>660</v>
@@ -15948,7 +16517,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="C186">
         <v>666</v>
@@ -16028,7 +16597,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>9</v>
+        <v>204</v>
       </c>
       <c r="C187">
         <v>1086</v>
@@ -16108,7 +16677,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C188">
         <v>620</v>
@@ -16188,7 +16757,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="C189">
         <v>923</v>
@@ -16268,7 +16837,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="C190">
         <v>442</v>
@@ -16348,7 +16917,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="C191">
         <v>1004</v>
@@ -16428,7 +16997,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="C192">
         <v>723</v>
@@ -16508,7 +17077,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="C193">
         <v>953</v>
@@ -16588,7 +17157,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="C194">
         <v>762</v>
@@ -16668,7 +17237,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="C195">
         <v>768</v>
@@ -16748,7 +17317,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="C196">
         <v>617</v>
@@ -16828,7 +17397,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="C197">
         <v>984</v>
@@ -16908,7 +17477,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="C198">
         <v>432</v>
@@ -16988,7 +17557,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>138</v>
+        <v>214</v>
       </c>
       <c r="C199">
         <v>660</v>
@@ -17068,7 +17637,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>61</v>
+        <v>215</v>
       </c>
       <c r="C200">
         <v>864</v>
@@ -17148,7 +17717,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>23</v>
+        <v>216</v>
       </c>
       <c r="C201">
         <v>927</v>
@@ -17228,7 +17797,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="C202">
         <v>988</v>
@@ -17308,7 +17877,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="C203">
         <v>983</v>
@@ -17388,7 +17957,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="C204">
         <v>1161</v>
@@ -17468,7 +18037,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>141</v>
+        <v>220</v>
       </c>
       <c r="C205">
         <v>967</v>
@@ -17548,7 +18117,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>142</v>
+        <v>221</v>
       </c>
       <c r="C206">
         <v>876</v>
@@ -17628,7 +18197,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>143</v>
+        <v>222</v>
       </c>
       <c r="C207">
         <v>594</v>
@@ -17708,7 +18277,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>17</v>
+        <v>223</v>
       </c>
       <c r="C208">
         <v>596</v>
@@ -17788,7 +18357,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="C209">
         <v>1057</v>
@@ -17868,7 +18437,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>144</v>
+        <v>225</v>
       </c>
       <c r="C210">
         <v>926</v>
@@ -17948,7 +18517,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>145</v>
+        <v>226</v>
       </c>
       <c r="C211">
         <v>827</v>
@@ -18028,7 +18597,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="C212">
         <v>526</v>
@@ -18108,7 +18677,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>29</v>
+        <v>228</v>
       </c>
       <c r="C213">
         <v>790</v>
@@ -18188,7 +18757,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>146</v>
+        <v>229</v>
       </c>
       <c r="C214">
         <v>637</v>
@@ -18268,7 +18837,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c r="C215">
         <v>599</v>
@@ -18348,7 +18917,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>147</v>
+        <v>231</v>
       </c>
       <c r="C216">
         <v>1050</v>
@@ -18428,7 +18997,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="C217">
         <v>1063</v>
@@ -18508,7 +19077,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="C218">
         <v>1160</v>
@@ -18588,7 +19157,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="C219">
         <v>1049</v>
@@ -18668,7 +19237,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="C220">
         <v>1099</v>
@@ -18748,7 +19317,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="C221">
         <v>936</v>
@@ -18828,7 +19397,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="C222">
         <v>1092</v>
@@ -18908,7 +19477,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="C223">
         <v>899</v>
@@ -18988,7 +19557,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>152</v>
+        <v>239</v>
       </c>
       <c r="C224">
         <v>765</v>
@@ -19068,7 +19637,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="C225">
         <v>584</v>
@@ -19148,7 +19717,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="C226">
         <v>761</v>
@@ -19228,7 +19797,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="C227">
         <v>787</v>
@@ -19308,7 +19877,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="C228">
         <v>744</v>
@@ -19388,7 +19957,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="C229">
         <v>798</v>
@@ -19468,7 +20037,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="C230">
         <v>647</v>
@@ -19548,7 +20117,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="C231">
         <v>724</v>
@@ -19628,7 +20197,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="C232">
         <v>1146</v>
@@ -19708,7 +20277,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="C233">
         <v>959</v>
@@ -19788,7 +20357,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="C234">
         <v>840</v>
@@ -19868,7 +20437,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="C235">
         <v>957</v>
@@ -19948,7 +20517,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>26</v>
+        <v>250</v>
       </c>
       <c r="C236">
         <v>926</v>
@@ -20028,7 +20597,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="C237">
         <v>757</v>
@@ -20108,7 +20677,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="C238">
         <v>913</v>
@@ -20188,7 +20757,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="C239">
         <v>557</v>
@@ -20268,7 +20837,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>61</v>
+        <v>253</v>
       </c>
       <c r="C240">
         <v>785</v>
@@ -20348,7 +20917,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>53</v>
+        <v>254</v>
       </c>
       <c r="C241">
         <v>834</v>
@@ -20428,7 +20997,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="C242">
         <v>970</v>
@@ -20508,7 +21077,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>160</v>
+        <v>256</v>
       </c>
       <c r="C243">
         <v>879</v>
@@ -20588,7 +21157,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="C244">
         <v>575</v>
@@ -20668,7 +21237,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="C245">
         <v>673</v>
@@ -20748,7 +21317,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="C246">
         <v>869</v>
@@ -20828,7 +21397,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>167</v>
+        <v>260</v>
       </c>
       <c r="C247">
         <v>869</v>
@@ -20908,7 +21477,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="C248">
         <v>732</v>
@@ -20988,7 +21557,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>169</v>
+        <v>262</v>
       </c>
       <c r="C249">
         <v>786</v>
@@ -21068,7 +21637,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="C250">
         <v>717</v>
@@ -21148,7 +21717,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="C251">
         <v>713</v>
@@ -21228,7 +21797,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="C252">
         <v>1121</v>
@@ -21308,7 +21877,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>129</v>
+        <v>266</v>
       </c>
       <c r="C253">
         <v>1120</v>
@@ -21388,7 +21957,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="C254">
         <v>907</v>
@@ -21468,7 +22037,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="C255">
         <v>903</v>
@@ -21548,7 +22117,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="C256">
         <v>770</v>
@@ -21628,7 +22197,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>61</v>
+        <v>270</v>
       </c>
       <c r="C257">
         <v>883</v>
@@ -21708,7 +22277,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>175</v>
+        <v>271</v>
       </c>
       <c r="C258">
         <v>802</v>
@@ -21788,7 +22357,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>176</v>
+        <v>272</v>
       </c>
       <c r="C259">
         <v>739</v>
@@ -21868,7 +22437,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>177</v>
+        <v>273</v>
       </c>
       <c r="C260">
         <v>1067</v>
@@ -21948,7 +22517,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="C261">
         <v>979</v>
@@ -22028,7 +22597,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>171</v>
+        <v>275</v>
       </c>
       <c r="C262">
         <v>797</v>
@@ -22108,7 +22677,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>129</v>
+        <v>276</v>
       </c>
       <c r="C263">
         <v>902</v>
@@ -22188,7 +22757,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>178</v>
+        <v>277</v>
       </c>
       <c r="C264">
         <v>611</v>
@@ -22268,7 +22837,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>129</v>
+        <v>278</v>
       </c>
       <c r="C265">
         <v>638</v>
@@ -22348,7 +22917,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>129</v>
+        <v>279</v>
       </c>
       <c r="C266">
         <v>1044</v>
@@ -22428,7 +22997,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="C267">
         <v>865</v>
@@ -22508,7 +23077,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>86</v>
+        <v>281</v>
       </c>
       <c r="C268">
         <v>605</v>
@@ -22588,7 +23157,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>136</v>
+        <v>282</v>
       </c>
       <c r="C269">
         <v>832</v>
@@ -22668,7 +23237,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>136</v>
+        <v>283</v>
       </c>
       <c r="C270">
         <v>784</v>
@@ -22748,7 +23317,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="C271">
         <v>1019</v>
@@ -22828,7 +23397,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="C272">
         <v>1009</v>
@@ -22908,7 +23477,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>41</v>
+        <v>286</v>
       </c>
       <c r="C273">
         <v>746</v>
@@ -22988,7 +23557,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="C274">
         <v>992</v>
@@ -23068,7 +23637,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="C275">
         <v>1045</v>
@@ -23148,7 +23717,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>183</v>
+        <v>289</v>
       </c>
       <c r="C276">
         <v>732</v>
@@ -23228,7 +23797,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="C277">
         <v>756</v>
@@ -23308,7 +23877,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="C278">
         <v>734</v>
@@ -23388,7 +23957,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="C279">
         <v>788</v>
@@ -23468,7 +24037,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="C280">
         <v>895</v>
@@ -23548,7 +24117,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>40</v>
+        <v>294</v>
       </c>
       <c r="C281">
         <v>1070</v>
@@ -23628,7 +24197,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>188</v>
+        <v>295</v>
       </c>
       <c r="C282">
         <v>721</v>
@@ -23708,7 +24277,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>188</v>
+        <v>296</v>
       </c>
       <c r="C283">
         <v>626</v>
@@ -23788,7 +24357,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>189</v>
+        <v>297</v>
       </c>
       <c r="C284">
         <v>928</v>
@@ -23868,7 +24437,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>25</v>
+        <v>298</v>
       </c>
       <c r="C285">
         <v>726</v>
@@ -23948,7 +24517,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
       <c r="C286">
         <v>514</v>
@@ -24028,7 +24597,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="C287">
         <v>736</v>
@@ -24108,7 +24677,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>191</v>
+        <v>301</v>
       </c>
       <c r="C288">
         <v>767</v>
@@ -24188,7 +24757,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>172</v>
+        <v>302</v>
       </c>
       <c r="C289">
         <v>1115</v>
@@ -24268,7 +24837,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>173</v>
+        <v>303</v>
       </c>
       <c r="C290">
         <v>944</v>
@@ -24348,7 +24917,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>192</v>
+        <v>304</v>
       </c>
       <c r="C291">
         <v>766</v>
@@ -24428,7 +24997,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>193</v>
+        <v>305</v>
       </c>
       <c r="C292">
         <v>705</v>
@@ -24508,7 +25077,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>194</v>
+        <v>306</v>
       </c>
       <c r="C293">
         <v>963</v>
@@ -24588,7 +25157,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>195</v>
+        <v>307</v>
       </c>
       <c r="C294">
         <v>732</v>
@@ -24668,7 +25237,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>196</v>
+        <v>308</v>
       </c>
       <c r="C295">
         <v>717</v>
@@ -24748,7 +25317,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>197</v>
+        <v>309</v>
       </c>
       <c r="C296">
         <v>962</v>
@@ -24828,7 +25397,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>198</v>
+        <v>310</v>
       </c>
       <c r="C297">
         <v>945</v>
@@ -24908,7 +25477,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>198</v>
+        <v>311</v>
       </c>
       <c r="C298">
         <v>925</v>
@@ -24988,7 +25557,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="C299">
         <v>932</v>
@@ -25068,7 +25637,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>199</v>
+        <v>312</v>
       </c>
       <c r="C300">
         <v>925</v>
@@ -25148,7 +25717,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>4</v>
+        <v>313</v>
       </c>
       <c r="C301">
         <v>613</v>
@@ -25228,7 +25797,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>5</v>
+        <v>313</v>
       </c>
       <c r="C302">
         <v>595</v>
@@ -25308,7 +25877,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>200</v>
+        <v>313</v>
       </c>
       <c r="C303">
         <v>890</v>
@@ -25388,7 +25957,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>201</v>
+        <v>313</v>
       </c>
       <c r="C304">
         <v>989</v>
@@ -25468,7 +26037,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>202</v>
+        <v>313</v>
       </c>
       <c r="C305">
         <v>1004</v>
@@ -25548,7 +26117,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>138</v>
+        <v>313</v>
       </c>
       <c r="C306">
         <v>864</v>
@@ -25628,7 +26197,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>203</v>
+        <v>313</v>
       </c>
       <c r="C307">
         <v>826</v>
@@ -25708,7 +26277,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="C308">
         <v>814</v>
@@ -25788,7 +26357,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>204</v>
+        <v>315</v>
       </c>
       <c r="C309">
         <v>699</v>
@@ -25868,7 +26437,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>204</v>
+        <v>316</v>
       </c>
       <c r="C310">
         <v>690</v>
@@ -25948,7 +26517,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="C311">
         <v>1004</v>
@@ -26028,7 +26597,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>205</v>
+        <v>318</v>
       </c>
       <c r="C312">
         <v>902</v>
@@ -26108,7 +26677,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>206</v>
+        <v>319</v>
       </c>
       <c r="C313">
         <v>524</v>
@@ -26188,7 +26757,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>207</v>
+        <v>320</v>
       </c>
       <c r="C314">
         <v>1011</v>
@@ -26268,7 +26837,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="C315">
         <v>1002</v>
@@ -26348,7 +26917,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="C316">
         <v>1098</v>
@@ -26428,7 +26997,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>209</v>
+        <v>323</v>
       </c>
       <c r="C317">
         <v>670</v>
@@ -26508,7 +27077,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>210</v>
+        <v>324</v>
       </c>
       <c r="C318">
         <v>663</v>
@@ -26588,7 +27157,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>211</v>
+        <v>325</v>
       </c>
       <c r="C319">
         <v>705</v>
@@ -26668,7 +27237,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>211</v>
+        <v>325</v>
       </c>
       <c r="C320">
         <v>673</v>
@@ -26748,7 +27317,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>129</v>
+        <v>325</v>
       </c>
       <c r="C321">
         <v>811</v>
@@ -26828,7 +27397,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>129</v>
+        <v>325</v>
       </c>
       <c r="C322">
         <v>801</v>
@@ -26908,7 +27477,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>61</v>
+        <v>325</v>
       </c>
       <c r="C323">
         <v>739</v>
@@ -26988,7 +27557,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>212</v>
+        <v>325</v>
       </c>
       <c r="C324">
         <v>1095</v>
@@ -27068,7 +27637,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>100</v>
+        <v>326</v>
       </c>
       <c r="C325">
         <v>773</v>
@@ -27148,7 +27717,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C326">
         <v>816</v>
@@ -27228,7 +27797,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>194</v>
+        <v>328</v>
       </c>
       <c r="C327">
         <v>428</v>
@@ -27308,7 +27877,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>214</v>
+        <v>329</v>
       </c>
       <c r="C328">
         <v>803</v>
@@ -27388,7 +27957,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="C329">
         <v>851</v>
@@ -27468,7 +28037,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>41</v>
+        <v>331</v>
       </c>
       <c r="C330">
         <v>772</v>
@@ -27548,7 +28117,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>61</v>
+        <v>332</v>
       </c>
       <c r="C331">
         <v>679</v>
@@ -27628,7 +28197,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>4</v>
+        <v>333</v>
       </c>
       <c r="C332">
         <v>899</v>
@@ -27708,7 +28277,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>5</v>
+        <v>334</v>
       </c>
       <c r="C333">
         <v>787</v>
@@ -27788,7 +28357,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>212</v>
+        <v>335</v>
       </c>
       <c r="C334">
         <v>454</v>
@@ -27868,7 +28437,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>215</v>
+        <v>336</v>
       </c>
       <c r="C335">
         <v>797</v>
@@ -27948,7 +28517,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>215</v>
+        <v>337</v>
       </c>
       <c r="C336">
         <v>731</v>
@@ -28028,7 +28597,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="C337">
         <v>508</v>
@@ -28108,7 +28677,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>217</v>
+        <v>339</v>
       </c>
       <c r="C338">
         <v>872</v>
@@ -28188,7 +28757,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
       <c r="C339">
         <v>457</v>
@@ -28268,7 +28837,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>219</v>
+        <v>341</v>
       </c>
       <c r="C340">
         <v>743</v>
@@ -28348,7 +28917,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="C341">
         <v>922</v>
@@ -28428,7 +28997,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>71</v>
+        <v>343</v>
       </c>
       <c r="C342">
         <v>643</v>
@@ -28508,7 +29077,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>71</v>
+        <v>344</v>
       </c>
       <c r="C343">
         <v>975</v>
@@ -28588,7 +29157,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>200</v>
+        <v>345</v>
       </c>
       <c r="C344">
         <v>1118</v>
@@ -28668,7 +29237,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>221</v>
+        <v>346</v>
       </c>
       <c r="C345">
         <v>651</v>
@@ -28748,7 +29317,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>222</v>
+        <v>346</v>
       </c>
       <c r="C346">
         <v>594</v>
@@ -28828,7 +29397,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>223</v>
+        <v>346</v>
       </c>
       <c r="C347">
         <v>1076</v>
@@ -28908,7 +29477,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>224</v>
+        <v>347</v>
       </c>
       <c r="C348">
         <v>685</v>
@@ -28988,7 +29557,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>153</v>
+        <v>348</v>
       </c>
       <c r="C349">
         <v>576</v>
@@ -29068,7 +29637,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>225</v>
+        <v>349</v>
       </c>
       <c r="C350">
         <v>872</v>
@@ -29148,7 +29717,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="C351">
         <v>907</v>
@@ -29228,7 +29797,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>226</v>
+        <v>351</v>
       </c>
       <c r="C352">
         <v>1089</v>
@@ -29308,7 +29877,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>227</v>
+        <v>352</v>
       </c>
       <c r="C353">
         <v>627</v>
@@ -29388,7 +29957,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>228</v>
+        <v>353</v>
       </c>
       <c r="C354">
         <v>673</v>
@@ -29468,7 +30037,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>229</v>
+        <v>354</v>
       </c>
       <c r="C355">
         <v>730</v>
@@ -29548,7 +30117,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="C356">
         <v>549</v>
@@ -29628,7 +30197,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>231</v>
+        <v>356</v>
       </c>
       <c r="C357">
         <v>1011</v>
@@ -29708,7 +30277,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>148</v>
+        <v>357</v>
       </c>
       <c r="C358">
         <v>1055</v>
@@ -29788,7 +30357,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="C359">
         <v>1125</v>
@@ -29868,7 +30437,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="C360">
         <v>1115</v>
@@ -29948,7 +30517,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>40</v>
+        <v>360</v>
       </c>
       <c r="C361">
         <v>1028</v>
@@ -30028,7 +30597,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>40</v>
+        <v>361</v>
       </c>
       <c r="C362">
         <v>1000</v>
@@ -30108,7 +30677,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="C363">
         <v>936</v>
@@ -30188,7 +30757,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>235</v>
+        <v>363</v>
       </c>
       <c r="C364">
         <v>1080</v>
@@ -30268,7 +30837,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>236</v>
+        <v>364</v>
       </c>
       <c r="C365">
         <v>1101</v>
@@ -30348,7 +30917,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>237</v>
+        <v>365</v>
       </c>
       <c r="C366">
         <v>1073</v>
@@ -30428,7 +30997,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>237</v>
+        <v>366</v>
       </c>
       <c r="C367">
         <v>1077</v>
@@ -30508,7 +31077,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>237</v>
+        <v>367</v>
       </c>
       <c r="C368">
         <v>1042</v>
@@ -30588,7 +31157,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>237</v>
+        <v>368</v>
       </c>
       <c r="C369">
         <v>1024</v>
@@ -30668,7 +31237,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>238</v>
+        <v>369</v>
       </c>
       <c r="C370">
         <v>987</v>
@@ -30748,7 +31317,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>239</v>
+        <v>370</v>
       </c>
       <c r="C371">
         <v>887</v>
@@ -30828,7 +31397,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>240</v>
+        <v>371</v>
       </c>
       <c r="C372">
         <v>661</v>
@@ -30908,7 +31477,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>241</v>
+        <v>372</v>
       </c>
       <c r="C373">
         <v>803</v>
@@ -30988,7 +31557,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>242</v>
+        <v>373</v>
       </c>
       <c r="C374">
         <v>534</v>
@@ -31068,7 +31637,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>243</v>
+        <v>374</v>
       </c>
       <c r="C375">
         <v>1183</v>
@@ -31148,7 +31717,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>244</v>
+        <v>375</v>
       </c>
       <c r="C376">
         <v>1177</v>
@@ -31228,7 +31797,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>245</v>
+        <v>376</v>
       </c>
       <c r="C377">
         <v>1004</v>
@@ -31308,7 +31877,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>246</v>
+        <v>377</v>
       </c>
       <c r="C378">
         <v>1027</v>
@@ -31388,7 +31957,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>247</v>
+        <v>378</v>
       </c>
       <c r="C379">
         <v>1153</v>
@@ -31468,7 +32037,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>248</v>
+        <v>379</v>
       </c>
       <c r="C380">
         <v>790</v>
@@ -31548,7 +32117,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>26</v>
+        <v>380</v>
       </c>
       <c r="C381">
         <v>1109</v>
@@ -31628,7 +32197,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>249</v>
+        <v>381</v>
       </c>
       <c r="C382">
         <v>1038</v>
@@ -31708,7 +32277,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>250</v>
+        <v>382</v>
       </c>
       <c r="C383">
         <v>974</v>
@@ -31788,7 +32357,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>251</v>
+        <v>383</v>
       </c>
       <c r="C384">
         <v>1150</v>
@@ -31868,7 +32437,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>251</v>
+        <v>384</v>
       </c>
       <c r="C385">
         <v>1017</v>
@@ -31948,7 +32517,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>251</v>
+        <v>385</v>
       </c>
       <c r="C386">
         <v>1047</v>
@@ -32028,7 +32597,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>251</v>
+        <v>386</v>
       </c>
       <c r="C387">
         <v>866</v>
@@ -32108,7 +32677,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>252</v>
+        <v>387</v>
       </c>
       <c r="C388">
         <v>1006</v>
@@ -32188,7 +32757,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>253</v>
+        <v>388</v>
       </c>
       <c r="C389">
         <v>770</v>
@@ -32268,7 +32837,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>254</v>
+        <v>389</v>
       </c>
       <c r="C390">
         <v>664</v>
@@ -32348,7 +32917,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>255</v>
+        <v>390</v>
       </c>
       <c r="C391">
         <v>593</v>
@@ -32428,7 +32997,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>256</v>
+        <v>391</v>
       </c>
       <c r="C392">
         <v>1158</v>
@@ -32508,7 +33077,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>257</v>
+        <v>392</v>
       </c>
       <c r="C393">
         <v>917</v>
@@ -32588,7 +33157,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>258</v>
+        <v>393</v>
       </c>
       <c r="C394">
         <v>884</v>
@@ -32668,7 +33237,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>136</v>
+        <v>394</v>
       </c>
       <c r="C395">
         <v>0</v>
@@ -32748,7 +33317,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>137</v>
+        <v>395</v>
       </c>
       <c r="C396">
         <v>554</v>
@@ -32828,7 +33397,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>259</v>
+        <v>396</v>
       </c>
       <c r="C397">
         <v>823</v>
@@ -32908,7 +33477,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>260</v>
+        <v>397</v>
       </c>
       <c r="C398">
         <v>785</v>
@@ -32988,7 +33557,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>260</v>
+        <v>398</v>
       </c>
       <c r="C399">
         <v>871</v>
@@ -33068,7 +33637,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>261</v>
+        <v>399</v>
       </c>
       <c r="C400">
         <v>689</v>
@@ -33148,7 +33717,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>169</v>
+        <v>400</v>
       </c>
       <c r="C401">
         <v>731</v>
@@ -33228,7 +33797,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>61</v>
+        <v>401</v>
       </c>
       <c r="C402">
         <v>1122</v>
@@ -33308,7 +33877,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>262</v>
+        <v>402</v>
       </c>
       <c r="C403">
         <v>1077</v>
@@ -33388,7 +33957,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>262</v>
+        <v>403</v>
       </c>
       <c r="C404">
         <v>1000</v>
@@ -33468,7 +34037,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>263</v>
+        <v>404</v>
       </c>
       <c r="C405">
         <v>1059</v>
@@ -33548,7 +34117,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>100</v>
+        <v>405</v>
       </c>
       <c r="C406">
         <v>630</v>
@@ -33628,7 +34197,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>213</v>
+        <v>406</v>
       </c>
       <c r="C407">
         <v>622</v>
@@ -33708,7 +34277,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>100</v>
+        <v>407</v>
       </c>
       <c r="C408">
         <v>797</v>
@@ -33788,7 +34357,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>213</v>
+        <v>408</v>
       </c>
       <c r="C409">
         <v>826</v>
@@ -33868,7 +34437,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>264</v>
+        <v>409</v>
       </c>
       <c r="C410">
         <v>645</v>
@@ -33948,7 +34517,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>264</v>
+        <v>410</v>
       </c>
       <c r="C411">
         <v>733</v>
@@ -34028,7 +34597,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>265</v>
+        <v>411</v>
       </c>
       <c r="C412">
         <v>1058</v>
@@ -34108,7 +34677,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>203</v>
+        <v>412</v>
       </c>
       <c r="C413">
         <v>1055</v>
@@ -34188,7 +34757,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>203</v>
+        <v>413</v>
       </c>
       <c r="C414">
         <v>1102</v>
@@ -34268,7 +34837,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>4</v>
+        <v>414</v>
       </c>
       <c r="C415">
         <v>892</v>
@@ -34348,7 +34917,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>4</v>
+        <v>415</v>
       </c>
       <c r="C416">
         <v>737</v>
@@ -34428,7 +34997,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>4</v>
+        <v>416</v>
       </c>
       <c r="C417">
         <v>868</v>
@@ -34508,7 +35077,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>86</v>
+        <v>417</v>
       </c>
       <c r="C418">
         <v>450</v>
@@ -34588,7 +35157,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>71</v>
+        <v>418</v>
       </c>
       <c r="C419">
         <v>988</v>
@@ -34668,7 +35237,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>70</v>
+        <v>419</v>
       </c>
       <c r="C420">
         <v>982</v>
@@ -34748,7 +35317,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>71</v>
+        <v>420</v>
       </c>
       <c r="C421">
         <v>1013</v>
@@ -34828,7 +35397,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>71</v>
+        <v>421</v>
       </c>
       <c r="C422">
         <v>1004</v>
